--- a/AAII_Financials/Quarterly/FRVWY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRVWY_QTR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Quarterly/FRVWY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRVWY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>FRVWY</t>
   </si>
@@ -656,62 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -739,8 +746,14 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -768,8 +781,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -797,8 +816,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +835,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,8 +866,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,8 +901,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -897,8 +936,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -926,8 +971,14 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,8 +987,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -965,8 +1018,14 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -994,8 +1053,14 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,8 +1072,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1036,8 +1103,14 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1065,8 +1138,14 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1094,8 +1173,14 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1123,8 +1208,14 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1152,8 +1243,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,8 +1278,14 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1210,8 +1313,14 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1239,8 +1348,14 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1383,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1418,14 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1453,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,8 +1488,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1384,8 +1523,14 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1413,8 +1558,14 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,8 +1593,14 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1471,42 +1628,54 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1687,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,37 +1702,45 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>119100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>180800</v>
+      </c>
+      <c r="F41" s="3">
         <v>58000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>39900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>62500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>15600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1589,211 +1768,259 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>120500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>104300</v>
+      </c>
+      <c r="F43" s="3">
         <v>165300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>150800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>118600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>120000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>166200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>149600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>133500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>126800</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F44" s="3">
         <v>9500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>11400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>8500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>8000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>8900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>11400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>12300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
         <v>9000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>7200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>8800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>7900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>9500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>11400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>265000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>294900</v>
+      </c>
+      <c r="F46" s="3">
         <v>241800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>178100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>175800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>191900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>185700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>175300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>172800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>189200</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F47" s="3">
         <v>16800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>16200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>16600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>14000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>28500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>25300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>23100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>136700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>128000</v>
+      </c>
+      <c r="F48" s="3">
         <v>136000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>125800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>120200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>106400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>99900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>101400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>98800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>95500</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F49" s="3">
         <v>6200</v>
-      </c>
-      <c r="E49" s="3">
-        <v>6000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>6000</v>
       </c>
       <c r="G49" s="3">
         <v>6000</v>
       </c>
       <c r="H49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J49" s="3">
         <v>5000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>5100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>5100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +2048,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,37 +2083,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3000</v>
+        <v>5400</v>
       </c>
       <c r="E52" s="3">
-        <v>2400</v>
+        <v>4900</v>
       </c>
       <c r="F52" s="3">
         <v>3000</v>
       </c>
       <c r="G52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I52" s="3">
         <v>15600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>14000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>11600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>10800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,37 +2153,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>435800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>453000</v>
+      </c>
+      <c r="F54" s="3">
         <v>415000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>339600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>332700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>344100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>346900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>330300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>322500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>329200</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2207,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,182 +2222,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F57" s="3">
         <v>13800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>5500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>7100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>7900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E58" s="3">
         <v>7000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G58" s="3">
         <v>5200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>12400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>113700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>127600</v>
+      </c>
+      <c r="F59" s="3">
         <v>114200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>76100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>77700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>72600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>101600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>72300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>69300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>178100</v>
+      </c>
+      <c r="F60" s="3">
         <v>135000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>88900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>88900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>103600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>113900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>92500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>84800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>26800</v>
+      </c>
+      <c r="F61" s="3">
         <v>30600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>30200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>30800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>24200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>24000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>25800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>26800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F62" s="3">
         <v>9700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>7900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>7100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>7300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>7300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>7700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>7400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2463,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2498,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,37 +2533,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>205100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>240800</v>
+      </c>
+      <c r="F66" s="3">
         <v>201400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>148000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>145700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>154500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>171700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>151000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>144200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>154900</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2587,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2618,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2653,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2688,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,37 +2723,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>209100</v>
+      </c>
+      <c r="E72" s="3">
         <v>191300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
+        <v>191300</v>
+      </c>
+      <c r="G72" s="3">
         <v>169900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>165300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>167400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>154000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>157300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>156200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>153200</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2793,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2828,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,37 +2863,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>230700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>212300</v>
+      </c>
+      <c r="F76" s="3">
         <v>213600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>191600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>186900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>189600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>175200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>178900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>177900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>174000</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,42 +2933,54 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2619,8 +3008,14 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,37 +3027,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>4700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>4500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>4100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>4300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>4200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +3093,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +3128,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +3163,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +3198,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3233,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-58800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>138600</v>
+      </c>
+      <c r="F89" s="3">
         <v>59600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-15100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-19100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>70600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>13800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-6400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-22400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,37 +3287,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-10900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-10900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-8500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-8100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-9000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-7200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-8600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3353,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,37 +3388,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-10500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-11000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-8800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-7400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-9100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-6600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-8900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,37 +3442,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>2600</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>2600</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3508,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3543,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,37 +3578,49 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-4900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>6800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-3700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-6700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-3000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3151,33 +3648,45 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-69700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>127000</v>
+      </c>
+      <c r="F102" s="3">
         <v>48900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-30900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-21100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>59600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-10800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-34300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>42900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FRVWY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRVWY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>FRVWY</t>
   </si>
@@ -656,69 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,8 +756,11 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +794,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +832,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +850,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +886,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +924,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -942,8 +962,11 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1000,11 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,8 +1015,9 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1024,8 +1051,11 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1059,8 +1089,11 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,8 +1107,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1109,8 +1143,11 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1144,8 +1181,11 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,8 +1219,11 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1214,8 +1257,11 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1295,11 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,8 +1333,11 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1319,8 +1371,11 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1354,8 +1409,11 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1447,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1485,11 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,8 +1561,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1529,8 +1599,11 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1564,8 +1637,11 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,8 +1675,11 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1634,48 +1713,54 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,43 +1790,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>119300</v>
+      </c>
+      <c r="E41" s="3">
         <v>119100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>180800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>58000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>39900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>62500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1774,232 +1864,253 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>139800</v>
+      </c>
+      <c r="E43" s="3">
         <v>120500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>104300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>165300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>150800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>118600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>120000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>166200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>149600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>133500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>126800</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E44" s="3">
         <v>12300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E45" s="3">
         <v>13000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>283500</v>
+      </c>
+      <c r="E46" s="3">
         <v>265000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>294900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>241800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>178100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>175800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>191900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>185700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>175300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>172800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>189200</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E47" s="3">
         <v>13900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>16800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>25300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>23100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>165900</v>
+      </c>
+      <c r="E48" s="3">
         <v>136700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>128000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>136000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>125800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>120200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>106400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>99900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>101400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>98800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>95500</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E49" s="3">
         <v>5900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>6000</v>
       </c>
       <c r="H49" s="3">
         <v>6000</v>
@@ -2008,19 +2119,22 @@
         <v>6000</v>
       </c>
       <c r="J49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K49" s="3">
         <v>5000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>5100</v>
       </c>
       <c r="L49" s="3">
         <v>5100</v>
       </c>
       <c r="M49" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N49" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2206,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E52" s="3">
         <v>5400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2282,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>489800</v>
+      </c>
+      <c r="E54" s="3">
         <v>435800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>453000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>415000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>339600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>332700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>344100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>346900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>330300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>322500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>329200</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,218 +2354,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E57" s="3">
         <v>16300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E58" s="3">
         <v>6900</v>
-      </c>
-      <c r="E58" s="3">
-        <v>7000</v>
       </c>
       <c r="F58" s="3">
         <v>7000</v>
       </c>
       <c r="G58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H58" s="3">
         <v>5200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>116300</v>
+      </c>
+      <c r="E59" s="3">
         <v>113700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>127600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>114200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>76100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>77700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>72600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>101600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>72300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>69300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>138500</v>
+      </c>
+      <c r="E60" s="3">
         <v>136900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>178100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>135000</v>
-      </c>
-      <c r="G60" s="3">
-        <v>88900</v>
       </c>
       <c r="H60" s="3">
         <v>88900</v>
       </c>
       <c r="I60" s="3">
+        <v>88900</v>
+      </c>
+      <c r="J60" s="3">
         <v>103600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>113900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>92500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>84800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E61" s="3">
         <v>26900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>30600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>30200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>30800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>24200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>26800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E62" s="3">
         <v>10100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>7300</v>
       </c>
       <c r="J62" s="3">
         <v>7300</v>
       </c>
       <c r="K62" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L62" s="3">
         <v>7700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2694,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>223100</v>
+      </c>
+      <c r="E66" s="3">
         <v>205100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>240800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>201400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>148000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>145700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>154500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>171700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>151000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>144200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>154900</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2900,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>243200</v>
+      </c>
+      <c r="E72" s="3">
         <v>209100</v>
-      </c>
-      <c r="E72" s="3">
-        <v>191300</v>
       </c>
       <c r="F72" s="3">
         <v>191300</v>
       </c>
       <c r="G72" s="3">
+        <v>191300</v>
+      </c>
+      <c r="H72" s="3">
         <v>169900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>165300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>167400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>154000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>157300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>156200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>153200</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3052,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>266700</v>
+      </c>
+      <c r="E76" s="3">
         <v>230700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>212300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>213600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>191600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>186900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>189600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>175200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>178900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>177900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>174000</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,48 +3128,54 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3014,8 +3209,11 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3227,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E83" s="3">
         <v>5200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>4800</v>
       </c>
       <c r="G83" s="3">
         <v>4800</v>
       </c>
       <c r="H83" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I83" s="3">
         <v>4700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3453,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-58800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>138600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>59600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-15100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>70600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3509,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-10900</v>
       </c>
       <c r="G91" s="3">
         <v>-10900</v>
       </c>
       <c r="H91" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="I91" s="3">
         <v>-8500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3621,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,43 +3677,47 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>2600</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>2600</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,43 +3827,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3654,39 +3903,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-69700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>127000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>48900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>59600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-34300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>42900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FRVWY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRVWY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
   <si>
     <t>FRVWY</t>
   </si>
@@ -656,77 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -766,8 +773,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +820,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +867,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +890,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +933,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,8 +980,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,8 +1027,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1074,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,8 +1094,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1084,8 +1137,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1125,8 +1184,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,8 +1207,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1183,8 +1250,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1224,8 +1297,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1265,8 +1344,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1306,8 +1391,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,8 +1438,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,8 +1485,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1429,8 +1532,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1470,8 +1579,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1626,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1673,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1720,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,8 +1767,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1675,8 +1814,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1716,8 +1861,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,8 +1908,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1798,54 +1955,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2030,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,57 +2049,65 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>272400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>312400</v>
+      </c>
+      <c r="F41" s="3">
         <v>145400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>119300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>119100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>180800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>58000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>39900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>62500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>15600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>8900</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -1960,295 +2139,343 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>107200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>97400</v>
+      </c>
+      <c r="F43" s="3">
         <v>153800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>139800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>120500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>104300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>165300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>150800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>118600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>120000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>166200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>149600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>133500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>126800</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>15900</v>
+      </c>
+      <c r="F44" s="3">
         <v>15200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>12900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>12300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>7300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>9500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>11400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>8500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>8000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>8900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>11400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>12300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F45" s="3">
         <v>10300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>11600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>13000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>9000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>7200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>8800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>7900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>9500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>11400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>414500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>438000</v>
+      </c>
+      <c r="F46" s="3">
         <v>324700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>283500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>265000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>294900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>241800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>178100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>175800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>191900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>185700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>175300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>172800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>189200</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>39500</v>
+      </c>
+      <c r="F47" s="3">
         <v>31800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>18900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>13900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>11700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>16800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>16200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>16600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>14000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>28500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>25300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>23100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>188700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>183000</v>
+      </c>
+      <c r="F48" s="3">
         <v>171100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>165900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>136700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>128000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>136000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>125800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>120200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>106400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>99900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>101400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>98800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>95500</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="E49" s="3">
         <v>6400</v>
       </c>
       <c r="F49" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G49" s="3">
+        <v>6400</v>
+      </c>
+      <c r="H49" s="3">
         <v>5900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>5700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>6200</v>
-      </c>
-      <c r="I49" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>6000</v>
       </c>
       <c r="K49" s="3">
         <v>6000</v>
       </c>
       <c r="L49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N49" s="3">
         <v>5000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>5100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>5100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2515,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,49 +2562,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F52" s="3">
         <v>2800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>4800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>5400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>4900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2400</v>
       </c>
       <c r="J52" s="3">
         <v>3000</v>
       </c>
       <c r="K52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M52" s="3">
         <v>15600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>14000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>11600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>10800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2656,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>664600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>676200</v>
+      </c>
+      <c r="F54" s="3">
         <v>547000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>489800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>435800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>453000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>415000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>339600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>332700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>344100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>346900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>330300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>322500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>329200</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2726,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,254 +2745,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F57" s="3">
         <v>16100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>14900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>16300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>13800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>7600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>7100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>7900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>9600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F58" s="3">
         <v>7000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>7200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>6900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>7000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>12400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>5900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>188500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>171200</v>
+      </c>
+      <c r="F59" s="3">
         <v>123000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>116300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>113700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>127600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>114200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>76100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>77700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>72600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>101600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>72300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>69300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>207600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>237600</v>
+      </c>
+      <c r="F60" s="3">
         <v>146100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>138500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>136900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>178100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>135000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>88900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>88900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>103600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>113900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>92500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>84800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>26600</v>
+      </c>
+      <c r="F61" s="3">
         <v>27200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>28100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>26900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>26800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>30600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>30200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>30800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>24200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>24000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>25800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>26800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>27500</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F62" s="3">
         <v>17400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>13600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>10100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>8800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>9700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>7900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>7100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>7300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>7300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>7700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>7400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3070,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3117,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3164,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>318100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>341300</v>
+      </c>
+      <c r="F66" s="3">
         <v>247100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>223100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>205100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>240800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>201400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>148000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>145700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>154500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>171700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>151000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>144200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>154900</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3234,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3277,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3324,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3371,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3418,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>324600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>311500</v>
+      </c>
+      <c r="F72" s="3">
         <v>277100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>243200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>209100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>191300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>191300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>169900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>165300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>167400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>154000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>157300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>156200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>153200</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3512,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3559,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3606,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>347700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>335600</v>
+      </c>
+      <c r="F76" s="3">
         <v>300600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>266700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>230700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>212300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>213600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>191600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>186900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>189600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>175200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>178900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>177900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>174000</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,54 +3700,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3410,8 +3799,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,49 +3822,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F83" s="3">
         <v>6100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>5500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>5200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>4900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>4800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>4800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>4700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>4500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>4100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>4300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>4200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3912,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3959,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4006,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4053,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +4100,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>200000</v>
+      </c>
+      <c r="F89" s="3">
         <v>44200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>22400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-58800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>138600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>59600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-15100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-19100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>70600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>13800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-6400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-22400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,49 +4170,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-9900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-22400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-9000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-8100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-10900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-10900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-8500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-8100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-9000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-7200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-8600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4260,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4307,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-16000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-23300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-9100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-8100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-10500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-11000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-8800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-7400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-9100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-6600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-8900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,49 +4377,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>7000</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>2600</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>2600</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4467,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4514,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,49 +4561,61 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-9200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-3500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-4900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>6800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-3700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-6700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-3000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4158,45 +4655,57 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>166900</v>
+      </c>
+      <c r="F102" s="3">
         <v>26200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-10100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-69700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>127000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>48900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-30900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-21100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>59600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-10800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-34300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>42900</v>
       </c>
     </row>
